--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -470,28 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.90693</v>
+        <v>17.79859</v>
       </c>
       <c r="D2" t="n">
-        <v>17.93258</v>
+        <v>17.32</v>
       </c>
       <c r="E2" t="n">
-        <v>17.83453</v>
+        <v>17.41964</v>
       </c>
       <c r="F2" t="n">
-        <v>59.03561</v>
+        <v>44.03729</v>
       </c>
       <c r="G2" t="n">
-        <v>44.4429</v>
+        <v>0.05432</v>
       </c>
       <c r="H2" t="n">
-        <v>90.58029000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.05307</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.89102</v>
+        <v>1.95867</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.53684</v>
+        <v>17.91713</v>
       </c>
       <c r="D3" t="n">
-        <v>17.53547</v>
+        <v>17.71526</v>
       </c>
       <c r="E3" t="n">
-        <v>17.53622</v>
+        <v>17.7391</v>
       </c>
       <c r="F3" t="n">
-        <v>58.38372</v>
+        <v>45.02395</v>
       </c>
       <c r="G3" t="n">
-        <v>44.64407</v>
+        <v>0.05322</v>
       </c>
       <c r="H3" t="n">
-        <v>89.25982999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.05379</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.97431</v>
+        <v>1.9188</v>
       </c>
     </row>
     <row r="4">
@@ -532,28 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.05903</v>
+        <v>17.99163</v>
       </c>
       <c r="D4" t="n">
-        <v>17.5952</v>
+        <v>17.78951</v>
       </c>
       <c r="E4" t="n">
-        <v>17.53775</v>
+        <v>17.85408</v>
       </c>
       <c r="F4" t="n">
-        <v>58.69042</v>
+        <v>45.43794</v>
       </c>
       <c r="G4" t="n">
-        <v>44.68555</v>
+        <v>0.05281</v>
       </c>
       <c r="H4" t="n">
-        <v>88.11100999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05348</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.89763</v>
+        <v>1.90257</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.86656</v>
+        <v>18.09278</v>
       </c>
       <c r="D5" t="n">
-        <v>17.7393</v>
+        <v>17.2238</v>
       </c>
       <c r="E5" t="n">
-        <v>17.69003</v>
+        <v>17.58288</v>
       </c>
       <c r="F5" t="n">
-        <v>57.49872</v>
+        <v>44.70241</v>
       </c>
       <c r="G5" t="n">
-        <v>45.18947</v>
+        <v>0.05407</v>
       </c>
       <c r="H5" t="n">
-        <v>89.45047</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.05387</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.91173</v>
+        <v>1.94634</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.58504</v>
+        <v>18.06333</v>
       </c>
       <c r="D6" t="n">
-        <v>17.31963</v>
+        <v>17.59437</v>
       </c>
       <c r="E6" t="n">
-        <v>17.82784</v>
+        <v>17.85226</v>
       </c>
       <c r="F6" t="n">
-        <v>58.66852</v>
+        <v>44.64242</v>
       </c>
       <c r="G6" t="n">
-        <v>45.23504</v>
+        <v>0.05488</v>
       </c>
       <c r="H6" t="n">
-        <v>89.90204</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.05423</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.94269</v>
+        <v>1.9273</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.55709</v>
+        <v>17.79594</v>
       </c>
       <c r="D7" t="n">
-        <v>17.23849</v>
+        <v>17.56284</v>
       </c>
       <c r="E7" t="n">
-        <v>17.57793</v>
+        <v>17.74462</v>
       </c>
       <c r="F7" t="n">
-        <v>58.51337</v>
+        <v>45.69689</v>
       </c>
       <c r="G7" t="n">
-        <v>45.68952</v>
+        <v>0.05387</v>
       </c>
       <c r="H7" t="n">
-        <v>88.56567</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.05411</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.9152</v>
+        <v>1.92395</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.99289</v>
+        <v>17.8848</v>
       </c>
       <c r="D8" t="n">
-        <v>17.91559</v>
+        <v>17.70513</v>
       </c>
       <c r="E8" t="n">
-        <v>17.43283</v>
+        <v>17.8469</v>
       </c>
       <c r="F8" t="n">
-        <v>59.28705</v>
+        <v>44.76314</v>
       </c>
       <c r="G8" t="n">
-        <v>44.43033</v>
+        <v>0.05302</v>
       </c>
       <c r="H8" t="n">
-        <v>88.43107999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.05395</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.92545</v>
+        <v>1.92634</v>
       </c>
     </row>
     <row r="9">
@@ -687,28 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.75711</v>
+        <v>17.89901</v>
       </c>
       <c r="D9" t="n">
-        <v>17.57127</v>
+        <v>17.39857</v>
       </c>
       <c r="E9" t="n">
-        <v>17.48837</v>
+        <v>17.60307</v>
       </c>
       <c r="F9" t="n">
-        <v>58.82298</v>
+        <v>45.3823</v>
       </c>
       <c r="G9" t="n">
-        <v>45.40947</v>
+        <v>0.05484</v>
       </c>
       <c r="H9" t="n">
-        <v>90.88558</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.05342</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.93673</v>
+        <v>1.91935</v>
       </c>
     </row>
     <row r="10">
@@ -718,28 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.86041</v>
+        <v>17.88416</v>
       </c>
       <c r="D10" t="n">
-        <v>17.78066</v>
+        <v>17.43534</v>
       </c>
       <c r="E10" t="n">
-        <v>17.6895</v>
+        <v>17.79496</v>
       </c>
       <c r="F10" t="n">
-        <v>58.76466</v>
+        <v>45.37336</v>
       </c>
       <c r="G10" t="n">
-        <v>44.75091</v>
+        <v>0.05307</v>
       </c>
       <c r="H10" t="n">
-        <v>89.9016</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.05396</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.93269</v>
+        <v>1.9054</v>
       </c>
     </row>
     <row r="11">
@@ -760,25 +696,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -796,28 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.6936</v>
+        <v>17.90708</v>
       </c>
       <c r="D12" t="n">
-        <v>17.65071</v>
+        <v>17.37667</v>
       </c>
       <c r="E12" t="n">
-        <v>17.63063</v>
+        <v>17.80342</v>
       </c>
       <c r="F12" t="n">
-        <v>58.58955</v>
+        <v>45.42496</v>
       </c>
       <c r="G12" t="n">
-        <v>45.42072</v>
+        <v>0.0536</v>
       </c>
       <c r="H12" t="n">
-        <v>91.25385</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.05423</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.91436</v>
+        <v>1.92539</v>
       </c>
     </row>
     <row r="13">
@@ -827,28 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.60196</v>
+        <v>17.85505</v>
       </c>
       <c r="D13" t="n">
-        <v>17.31801</v>
+        <v>17.68466</v>
       </c>
       <c r="E13" t="n">
-        <v>17.7801</v>
+        <v>17.70317</v>
       </c>
       <c r="F13" t="n">
-        <v>58.00305</v>
+        <v>45.0873</v>
       </c>
       <c r="G13" t="n">
-        <v>44.92446</v>
+        <v>0.05408</v>
       </c>
       <c r="H13" t="n">
-        <v>88.45735999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.05387</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.95469</v>
+        <v>1.90775</v>
       </c>
     </row>
     <row r="14">
@@ -858,28 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.63587</v>
+        <v>17.90541</v>
       </c>
       <c r="D14" t="n">
-        <v>17.72593</v>
+        <v>17.61535</v>
       </c>
       <c r="E14" t="n">
-        <v>17.31496</v>
+        <v>17.78278</v>
       </c>
       <c r="F14" t="n">
-        <v>58.89378</v>
+        <v>44.29664</v>
       </c>
       <c r="G14" t="n">
-        <v>45.32982</v>
+        <v>0.05424</v>
       </c>
       <c r="H14" t="n">
-        <v>89.43442</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.05296</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.94959</v>
+        <v>1.89765</v>
       </c>
     </row>
     <row r="15">
@@ -889,28 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.35529</v>
+        <v>17.8135</v>
       </c>
       <c r="D15" t="n">
-        <v>17.69728</v>
+        <v>17.67944</v>
       </c>
       <c r="E15" t="n">
-        <v>17.25598</v>
+        <v>17.76417</v>
       </c>
       <c r="F15" t="n">
-        <v>59.31512</v>
+        <v>44.78903</v>
       </c>
       <c r="G15" t="n">
-        <v>45.60373</v>
+        <v>0.05305</v>
       </c>
       <c r="H15" t="n">
-        <v>88.50047000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.05353</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.88292</v>
+        <v>1.94895</v>
       </c>
     </row>
     <row r="16">
@@ -920,28 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18.0761</v>
+        <v>17.83654</v>
       </c>
       <c r="D16" t="n">
-        <v>17.39492</v>
+        <v>17.70051</v>
       </c>
       <c r="E16" t="n">
-        <v>17.52428</v>
+        <v>17.75031</v>
       </c>
       <c r="F16" t="n">
-        <v>58.18306</v>
+        <v>44.32955</v>
       </c>
       <c r="G16" t="n">
-        <v>44.52413</v>
+        <v>0.05387</v>
       </c>
       <c r="H16" t="n">
-        <v>88.64845</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.05363</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.89455</v>
+        <v>1.89949</v>
       </c>
     </row>
     <row r="17">
@@ -951,28 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.89044</v>
+        <v>17.76146</v>
       </c>
       <c r="D17" t="n">
-        <v>17.74712</v>
+        <v>17.4311</v>
       </c>
       <c r="E17" t="n">
-        <v>17.95305</v>
+        <v>17.73776</v>
       </c>
       <c r="F17" t="n">
-        <v>59.03399</v>
+        <v>44.42209</v>
       </c>
       <c r="G17" t="n">
-        <v>44.93667</v>
+        <v>0.05393</v>
       </c>
       <c r="H17" t="n">
-        <v>91.48180000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.05356</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.95194</v>
+        <v>1.94841</v>
       </c>
     </row>
     <row r="18">
@@ -982,28 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.67166</v>
+        <v>17.95768</v>
       </c>
       <c r="D18" t="n">
-        <v>17.59042</v>
+        <v>17.19011</v>
       </c>
       <c r="E18" t="n">
-        <v>17.77692</v>
+        <v>17.70531</v>
       </c>
       <c r="F18" t="n">
-        <v>60.11551</v>
+        <v>45.46567</v>
       </c>
       <c r="G18" t="n">
-        <v>45.12976</v>
+        <v>0.05387</v>
       </c>
       <c r="H18" t="n">
-        <v>88.53164</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.05265</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.92691</v>
+        <v>1.90422</v>
       </c>
     </row>
     <row r="19">
@@ -1013,28 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.4167</v>
+        <v>18.19612</v>
       </c>
       <c r="D19" t="n">
-        <v>17.55565</v>
+        <v>17.70567</v>
       </c>
       <c r="E19" t="n">
-        <v>17.9504</v>
+        <v>17.78528</v>
       </c>
       <c r="F19" t="n">
-        <v>58.98588</v>
+        <v>45.00779</v>
       </c>
       <c r="G19" t="n">
-        <v>44.59484</v>
+        <v>0.05375</v>
       </c>
       <c r="H19" t="n">
-        <v>90.28722</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.05338</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.95292</v>
+        <v>1.91265</v>
       </c>
     </row>
     <row r="20">
@@ -1044,28 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.75621</v>
+        <v>17.66686</v>
       </c>
       <c r="D20" t="n">
-        <v>17.33563</v>
+        <v>17.43751</v>
       </c>
       <c r="E20" t="n">
-        <v>17.94296</v>
+        <v>17.66561</v>
       </c>
       <c r="F20" t="n">
-        <v>59.2152</v>
+        <v>44.86649</v>
       </c>
       <c r="G20" t="n">
-        <v>44.3107</v>
+        <v>0.05414</v>
       </c>
       <c r="H20" t="n">
-        <v>90.64427000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.05321</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.92107</v>
+        <v>1.93632</v>
       </c>
     </row>
     <row r="21">
@@ -1086,12 +958,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -1103,23 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.19757</v>
+        <v>17.01977</v>
       </c>
       <c r="D22" t="n">
-        <v>16.57378</v>
+        <v>16.35113</v>
       </c>
       <c r="E22" t="n">
-        <v>17.31854</v>
+        <v>16.98244</v>
       </c>
       <c r="F22" t="n">
-        <v>22.78259</v>
-      </c>
-      <c r="G22" t="n">
-        <v>36.11165</v>
+        <v>269.96509</v>
       </c>
     </row>
     <row r="23">
@@ -1129,19 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.50212</v>
+        <v>16.66973</v>
       </c>
       <c r="D23" t="n">
-        <v>16.75728</v>
+        <v>16.24878</v>
       </c>
       <c r="E23" t="n">
-        <v>17.58706</v>
+        <v>16.58681</v>
       </c>
       <c r="F23" t="n">
-        <v>23.28948</v>
-      </c>
-      <c r="G23" t="n">
-        <v>36.07179</v>
+        <v>270.883</v>
       </c>
     </row>
     <row r="24">
@@ -1151,19 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17.4466</v>
+        <v>16.66965</v>
       </c>
       <c r="D24" t="n">
-        <v>16.99904</v>
+        <v>16.40847</v>
       </c>
       <c r="E24" t="n">
-        <v>17.13505</v>
+        <v>16.49516</v>
       </c>
       <c r="F24" t="n">
-        <v>22.95185</v>
-      </c>
-      <c r="G24" t="n">
-        <v>36.20392</v>
+        <v>271.28014</v>
       </c>
     </row>
     <row r="25">
@@ -1173,19 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17.77744</v>
+        <v>16.82638</v>
       </c>
       <c r="D25" t="n">
-        <v>17.00836</v>
+        <v>16.5156</v>
       </c>
       <c r="E25" t="n">
-        <v>17.39487</v>
+        <v>16.53936</v>
       </c>
       <c r="F25" t="n">
-        <v>22.88706</v>
-      </c>
-      <c r="G25" t="n">
-        <v>36.99111</v>
+        <v>270.53848</v>
       </c>
     </row>
     <row r="26">
@@ -1195,19 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17.81409</v>
+        <v>16.71707</v>
       </c>
       <c r="D26" t="n">
-        <v>16.64866</v>
+        <v>16.50952</v>
       </c>
       <c r="E26" t="n">
-        <v>17.3553</v>
+        <v>16.56181</v>
       </c>
       <c r="F26" t="n">
-        <v>23.23459</v>
-      </c>
-      <c r="G26" t="n">
-        <v>35.16462</v>
+        <v>266.64722</v>
       </c>
     </row>
     <row r="27">
@@ -1217,19 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18.13408</v>
+        <v>16.70845</v>
       </c>
       <c r="D27" t="n">
-        <v>16.60732</v>
+        <v>16.48479</v>
       </c>
       <c r="E27" t="n">
-        <v>17.49317</v>
+        <v>16.61506</v>
       </c>
       <c r="F27" t="n">
-        <v>23.14127</v>
-      </c>
-      <c r="G27" t="n">
-        <v>36.49844</v>
+        <v>262.72546</v>
       </c>
     </row>
     <row r="28">
@@ -1239,19 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.58692</v>
+        <v>16.80396</v>
       </c>
       <c r="D28" t="n">
-        <v>16.78455</v>
+        <v>16.31367</v>
       </c>
       <c r="E28" t="n">
-        <v>17.29447</v>
+        <v>16.45806</v>
       </c>
       <c r="F28" t="n">
-        <v>22.82052</v>
-      </c>
-      <c r="G28" t="n">
-        <v>36.58152</v>
+        <v>271.20334</v>
       </c>
     </row>
     <row r="29">
@@ -1261,19 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.56848</v>
+        <v>16.88075</v>
       </c>
       <c r="D29" t="n">
-        <v>17.22426</v>
+        <v>16.37663</v>
       </c>
       <c r="E29" t="n">
-        <v>17.30841</v>
+        <v>16.69409</v>
       </c>
       <c r="F29" t="n">
-        <v>23.04024</v>
-      </c>
-      <c r="G29" t="n">
-        <v>35.82423</v>
+        <v>265.28651</v>
       </c>
     </row>
     <row r="30">
@@ -1283,60 +1126,42 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.37467</v>
+        <v>16.61459</v>
       </c>
       <c r="D30" t="n">
-        <v>17.0755</v>
+        <v>16.47654</v>
       </c>
       <c r="E30" t="n">
-        <v>17.32234</v>
+        <v>16.52493</v>
       </c>
       <c r="F30" t="n">
-        <v>22.74567</v>
-      </c>
-      <c r="G30" t="n">
-        <v>36.30624</v>
+        <v>267.1216</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -1348,32 +1173,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.79237</v>
+        <v>17.53803</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08542</v>
+        <v>16.97328</v>
       </c>
       <c r="E32" t="n">
-        <v>0.63456</v>
+        <v>17.26281</v>
       </c>
       <c r="F32" t="n">
-        <v>1.02926</v>
+        <v>22.63328</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11627</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.008019999999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.09877</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.13482</v>
+        <v>35.86982</v>
       </c>
     </row>
     <row r="33">
@@ -1383,28 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.79898</v>
+        <v>17.46686</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08513</v>
+        <v>16.84547</v>
       </c>
       <c r="E33" t="n">
-        <v>0.65154</v>
+        <v>17.25429</v>
       </c>
       <c r="F33" t="n">
-        <v>1.01678</v>
+        <v>22.94819</v>
       </c>
       <c r="G33" t="n">
-        <v>0.11336</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.007979999999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09907000000000001</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.1358</v>
+        <v>35.67144</v>
       </c>
     </row>
     <row r="34">
@@ -1414,28 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.80418</v>
+        <v>17.74822</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08537</v>
+        <v>16.73201</v>
       </c>
       <c r="E34" t="n">
-        <v>0.65484</v>
+        <v>17.1821</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0087</v>
+        <v>22.80485</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1133</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.007939999999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09907000000000001</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.1337</v>
+        <v>36.25379</v>
       </c>
     </row>
     <row r="35">
@@ -1445,28 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.79094</v>
+        <v>17.73021</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08449</v>
+        <v>17.19731</v>
       </c>
       <c r="E35" t="n">
-        <v>0.64967</v>
+        <v>17.24053</v>
       </c>
       <c r="F35" t="n">
-        <v>1.01272</v>
+        <v>22.64915</v>
       </c>
       <c r="G35" t="n">
-        <v>0.11733</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.00801</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09847</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.1325</v>
+        <v>35.72082</v>
       </c>
     </row>
     <row r="36">
@@ -1476,28 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.79653</v>
+        <v>17.70536</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08583</v>
+        <v>17.02241</v>
       </c>
       <c r="E36" t="n">
-        <v>0.64002</v>
+        <v>17.10701</v>
       </c>
       <c r="F36" t="n">
-        <v>1.02374</v>
+        <v>22.72564</v>
       </c>
       <c r="G36" t="n">
-        <v>0.11617</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09934999999999999</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.13505</v>
+        <v>36.26048</v>
       </c>
     </row>
     <row r="37">
@@ -1507,28 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.80084</v>
+        <v>17.9219</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08724</v>
+        <v>16.47267</v>
       </c>
       <c r="E37" t="n">
-        <v>0.64027</v>
+        <v>17.57627</v>
       </c>
       <c r="F37" t="n">
-        <v>1.03083</v>
+        <v>22.85885</v>
       </c>
       <c r="G37" t="n">
-        <v>0.11523</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.007979999999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09625</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.13397</v>
+        <v>36.65811</v>
       </c>
     </row>
     <row r="38">
@@ -1538,28 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.79792</v>
+        <v>17.43795</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08488999999999999</v>
+        <v>17.09982</v>
       </c>
       <c r="E38" t="n">
-        <v>0.64515</v>
+        <v>17.22716</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9967200000000001</v>
+        <v>23.59227</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1163</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.00805</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.09937</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.13275</v>
+        <v>36.32095</v>
       </c>
     </row>
     <row r="39">
@@ -1569,28 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.81266</v>
+        <v>17.55008</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08509</v>
+        <v>16.79084</v>
       </c>
       <c r="E39" t="n">
-        <v>0.63946</v>
+        <v>17.04539</v>
       </c>
       <c r="F39" t="n">
-        <v>1.03306</v>
+        <v>23.03348</v>
       </c>
       <c r="G39" t="n">
-        <v>0.11593</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.008059999999999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.0973</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.13464</v>
+        <v>36.21932</v>
       </c>
     </row>
     <row r="40">
@@ -1600,28 +1353,843 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.78746</v>
+        <v>17.53988</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08524</v>
+        <v>16.87271</v>
       </c>
       <c r="E40" t="n">
-        <v>0.64551</v>
+        <v>16.93733</v>
       </c>
       <c r="F40" t="n">
-        <v>1.00737</v>
+        <v>23.44244</v>
       </c>
       <c r="G40" t="n">
-        <v>0.11614</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.00805</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.0988</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.1343</v>
+        <v>36.266</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17.76114</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.96972</v>
+      </c>
+      <c r="E42" t="n">
+        <v>17.13211</v>
+      </c>
+      <c r="F42" t="n">
+        <v>23.36224</v>
+      </c>
+      <c r="G42" t="n">
+        <v>35.75747</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>17.87273</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.97653</v>
+      </c>
+      <c r="E43" t="n">
+        <v>17.69735</v>
+      </c>
+      <c r="F43" t="n">
+        <v>23.13846</v>
+      </c>
+      <c r="G43" t="n">
+        <v>36.14221</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17.65047</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.69951</v>
+      </c>
+      <c r="E44" t="n">
+        <v>17.51615</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.82832</v>
+      </c>
+      <c r="G44" t="n">
+        <v>36.37864</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>18.04829</v>
+      </c>
+      <c r="D45" t="n">
+        <v>17.00727</v>
+      </c>
+      <c r="E45" t="n">
+        <v>17.47626</v>
+      </c>
+      <c r="F45" t="n">
+        <v>23.48529</v>
+      </c>
+      <c r="G45" t="n">
+        <v>36.01418</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17.77378</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.99378</v>
+      </c>
+      <c r="E46" t="n">
+        <v>17.50648</v>
+      </c>
+      <c r="F46" t="n">
+        <v>23.31649</v>
+      </c>
+      <c r="G46" t="n">
+        <v>36.03041</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>17.32896</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.96345</v>
+      </c>
+      <c r="E47" t="n">
+        <v>17.22545</v>
+      </c>
+      <c r="F47" t="n">
+        <v>23.41519</v>
+      </c>
+      <c r="G47" t="n">
+        <v>35.35834</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17.55765</v>
+      </c>
+      <c r="D48" t="n">
+        <v>17.00603</v>
+      </c>
+      <c r="E48" t="n">
+        <v>17.2537</v>
+      </c>
+      <c r="F48" t="n">
+        <v>23.01133</v>
+      </c>
+      <c r="G48" t="n">
+        <v>36.6232</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.70762</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.96451</v>
+      </c>
+      <c r="E49" t="n">
+        <v>17.14084</v>
+      </c>
+      <c r="F49" t="n">
+        <v>23.22591</v>
+      </c>
+      <c r="G49" t="n">
+        <v>36.0955</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>17.93741</v>
+      </c>
+      <c r="D50" t="n">
+        <v>17.15208</v>
+      </c>
+      <c r="E50" t="n">
+        <v>17.39825</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.79396</v>
+      </c>
+      <c r="G50" t="n">
+        <v>36.55823</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.65462</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.1877</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.63976</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.17147</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.63617</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.164</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.64767</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.16444</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6442099999999999</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.19073</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.17825</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.64529</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.2039</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.65238</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.19134</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.65007</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.15945</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.62158</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.1879</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.64952</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.177</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.65992</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.19647</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.65329</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.19743</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.64372</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.1866</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.65607</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.18897</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.64402</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.16398</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.16759</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.63034</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.16208</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.79123</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08502</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.63691</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.00981</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.11476</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.008070000000000001</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.10091</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.13599</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.79393</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08502999999999999</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.6402600000000001</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.01074</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.11329</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.008019999999999999</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09699000000000001</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.13454</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.80043</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08577</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.62726</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.02214</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.11501</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00808</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09771000000000001</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.13242</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.7815</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08644</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.64002</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.02317</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.11559</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00813</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09929</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.13221</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.77783</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08523</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.63833</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.03345</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11387</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00812</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09789</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.13549</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.8083900000000001</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08452</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.64677</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.00497</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09841</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.13371</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.7928500000000001</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08479</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.64171</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.02712</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.11685</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00801</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09898999999999999</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.13449</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.8023</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08577</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.64107</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.01222</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.11559</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09878000000000001</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.13323</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.79643</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08548</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.63916</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.02737</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.11733</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00813</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09785000000000001</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.13254</v>
       </c>
     </row>
   </sheetData>
